--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
@@ -131,13 +131,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="A2:A2">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="A2:A2">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="C2:C2">
       <formula1>ISNUMBER(C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="E2:E2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE." sqref="E2:E2">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
@@ -131,13 +131,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="A2:A2">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="A2:A2">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="C2:C2">
       <formula1>ISNUMBER(C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE." sqref="E2:E2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE" sqref="E2:E2">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
@@ -131,13 +131,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="A2:A2">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="A2:A2">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="C2:C2">
       <formula1>ISNUMBER(C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="E2:E2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE" sqref="E2:E2">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
@@ -130,7 +130,7 @@
       <formula>LEN(TRIM(A2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="A2:A2">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
@@ -139,6 +139,10 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE" sqref="E2:E2">
       <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="F2:F2">
+      <formula1>2</formula1>
+      <formula2>2958465</formula2>
     </dataValidation>
   </dataValidations>
 </worksheet>

--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
@@ -140,7 +140,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE" sqref="E2:E2">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="F2:F2">
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time." sqref="F2:F2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
@@ -140,7 +140,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE" sqref="E2:E2">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time." sqref="F2:F2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" prompt="Date and time as yyyy-MM-dd HH:mm:ss" sqref="F2:F2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
@@ -140,7 +140,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE" sqref="E2:E2">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="F2:F2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" prompt="Date and time as yyyy-MM-dd HH:mm:ss" sqref="F2:F2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundDefaultsToNoInference.verified.xlsx
@@ -149,7 +149,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Name"/>
     <column index="2" property="Notes"/>
